--- a/results/Int Task Remove ACC 0.4/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_7_permute.xlsx
@@ -440,67 +440,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7971427361287591</v>
+        <v>0.7908877594239729</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7950487081745023</v>
+        <v>0.7830402371876324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7897509529860229</v>
+        <v>0.783706903854299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7919119017365523</v>
+        <v>0.783706903854299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7875984752223635</v>
+        <v>0.7831698432867429</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7717238458280389</v>
+        <v>0.7924091486658196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7214731046166878</v>
+        <v>0.7946954680220246</v>
       </c>
     </row>
     <row r="9">
@@ -510,467 +510,467 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7208064379500212</v>
+        <v>0.7950131300296485</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7141084286319357</v>
+        <v>0.7901541719610334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.711124099957645</v>
+        <v>0.7853578991952563</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7120770859805168</v>
+        <v>0.7902481999152902</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6915671325709445</v>
+        <v>0.7791884794578569</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6799474798814062</v>
+        <v>0.747430749682338</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6597280813214739</v>
+        <v>0.7379220669207962</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6600457433290978</v>
+        <v>0.7273451927149512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6329047013977128</v>
+        <v>0.7358009318085557</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6309987293519695</v>
+        <v>0.7133977128335451</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6352850487081745</v>
+        <v>0.7144133841592546</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6346497246929268</v>
+        <v>0.7124404913172384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6359830580262601</v>
+        <v>0.7097424819991529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.640269377382465</v>
+        <v>0.7114561626429479</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6267437526471834</v>
+        <v>0.6981855146124524</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6250927573062262</v>
+        <v>0.7200643795002117</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6250927573062262</v>
+        <v>0.7212952138924185</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6270969927996611</v>
+        <v>0.7332952138924185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6267479881406184</v>
+        <v>0.7123379923761118</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6278576874205845</v>
+        <v>0.7141770436255823</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5853604404913172</v>
+        <v>0.7238864887759424</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5853604404913172</v>
+        <v>0.716561626429479</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.595168149089369</v>
+        <v>0.7178636171113935</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5958348157560356</v>
+        <v>0.7020643795002117</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5851054637865312</v>
+        <v>0.7030800508259212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5798661584074545</v>
+        <v>0.6863778060144007</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5848818297331639</v>
+        <v>0.6727581533248623</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5922778483693351</v>
+        <v>0.6411969504447268</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.60170944515036</v>
+        <v>0.6261812791190173</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5965955103769589</v>
+        <v>0.6032367640830156</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6053917831427361</v>
+        <v>0.5892409995764507</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5970114358322745</v>
+        <v>0.579433290978399</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5926937738246506</v>
+        <v>0.5790529436679374</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5922778483693351</v>
+        <v>0.5760372723422279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5704701397712834</v>
+        <v>0.5767310461668784</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5778034731046167</v>
+        <v>0.5825158831003812</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5591368064379501</v>
+        <v>0.5500957221516307</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5637407878017789</v>
+        <v>0.5418449809402796</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5706624311732317</v>
+        <v>0.5291969504447268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5559644218551461</v>
+        <v>0.4971257941550191</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5591368064379501</v>
+        <v>0.508847945785684</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.55570944515036</v>
+        <v>0.5111071579839052</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.55570944515036</v>
+        <v>0.5186014400677679</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5572037272342227</v>
+        <v>0.5646556543837358</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5408860652265989</v>
+        <v>0.5686556543837358</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5428860652265989</v>
+        <v>0.5953096145700975</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5292037272342228</v>
+        <v>0.5737340110122829</v>
       </c>
     </row>
     <row r="56">
@@ -980,347 +980,347 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5085057179161372</v>
+        <v>0.5531512071156289</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5091723845828039</v>
+        <v>0.5782024565861923</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.50628208386277</v>
+        <v>0.5725201185938162</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5049487505294367</v>
+        <v>0.5730656501482423</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5071723845828039</v>
+        <v>0.571732316814909</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5101567132570944</v>
+        <v>0.5587793307920372</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5148860652265989</v>
+        <v>0.5587793307920372</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5166310885218128</v>
+        <v>0.5594773401101228</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5166310885218128</v>
+        <v>0.5385556967386701</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5205997458703939</v>
+        <v>0.552292249047014</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5216154171961034</v>
+        <v>0.5440415078356629</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5295840745446845</v>
+        <v>0.5486539601863617</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5292350698856417</v>
+        <v>0.5108233799237611</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5690072003388394</v>
+        <v>0.511141041931385</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5604701397712833</v>
+        <v>0.5110783566285473</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5232350698856417</v>
+        <v>0.5060626853028378</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5092350698856417</v>
+        <v>0.5053960186361711</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5109174078780178</v>
+        <v>0.5030783566285473</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5340897924608217</v>
+        <v>0.5030783566285473</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5029487505294367</v>
+        <v>0.5040626853028378</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5029487505294367</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5039330792037272</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5046624311732317</v>
+        <v>0.5000626853028378</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5057136806437951</v>
+        <v>0.5017136806437951</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5070156713257095</v>
+        <v>0.5021567132570944</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5043803473104617</v>
+        <v>0.5014188903007201</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5044743752647184</v>
+        <v>0.4992265988987717</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5025057179161372</v>
+        <v>0.500022871664549</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.501141041931385</v>
+        <v>0.5001168996188056</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5000313426514189</v>
+        <v>0.5001168996188056</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5000313426514189</v>
+        <v>0.5001168996188056</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996823379923761</v>
+        <v>0.4988775942397289</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.4856882676831851</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.484292249047014</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.484292249047014</v>
       </c>
     </row>
   </sheetData>
